--- a/results/v1.0.1/figures/2030/paper_figure_data_2030.xlsx
+++ b/results/v1.0.1/figures/2030/paper_figure_data_2030.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">F2</t>
   </si>
   <si>
-    <t xml:space="preserve">Figure 2. Capital and corporate revenue gains drive the increase; labor revenue falls mainly under slow adoption</t>
+    <t xml:space="preserve">Figure 2. Capital and corporate revenue gains drive increased revenues</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue change decomposed by type of income</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">F3</t>
   </si>
   <si>
-    <t xml:space="preserve">Figure 3. Revenue gains are driven by corporate and individual income tax revenue increases</t>
+    <t xml:space="preserve">Figure 3. Corporate and individual income tax revenues increase in most scenarios</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue change by tax instrument</t>
